--- a/Invesco/Invesco-MSCI-World.xlsx
+++ b/Invesco/Invesco-MSCI-World.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="211" documentId="13_ncr:1_{0128D462-482E-40FC-BDD9-3BC2319AD459}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A19B59EC-911D-4DE1-ADDB-417184AD1470}"/>
+  <xr:revisionPtr revIDLastSave="264" documentId="13_ncr:1_{0128D462-482E-40FC-BDD9-3BC2319AD459}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BF8B62EF-52ED-4899-9761-B6DD5DFCDF1B}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25800" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="26010" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Kosten" sheetId="2" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>MSCI World</t>
   </si>
@@ -58,19 +58,25 @@
     <t>Diff na kosten</t>
   </si>
   <si>
-    <t>Diff na kosten te groot voor dividendlek, zou kleiner moeten zijn</t>
-  </si>
-  <si>
     <t>AVG</t>
-  </si>
-  <si>
-    <t>Het is wel beter sinds 2018, of ging de TER toen omlaag?</t>
   </si>
   <si>
     <t>Perf</t>
   </si>
   <si>
-    <t>SPDR SWRD</t>
+    <t>Sinds 2018 werkt de USA swap weer</t>
+  </si>
+  <si>
+    <t>Diff na kosten te groot voor dividendlek, zou kleiner moeten zijn?</t>
+  </si>
+  <si>
+    <t>IWDA lek</t>
+  </si>
+  <si>
+    <t>2018-2025</t>
+  </si>
+  <si>
+    <t>Invesco kosten buiten TER</t>
   </si>
 </sst>
 </file>
@@ -626,7 +632,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -662,10 +668,16 @@
     <xf numFmtId="14" fontId="20" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="43">
     <cellStyle name="20% - Accent1" xfId="1" builtinId="30" customBuiltin="1"/>
@@ -692,25 +704,25 @@
     <cellStyle name="Accent4" xfId="22" builtinId="41" customBuiltin="1"/>
     <cellStyle name="Accent5" xfId="23" builtinId="45" customBuiltin="1"/>
     <cellStyle name="Accent6" xfId="24" builtinId="49" customBuiltin="1"/>
-    <cellStyle name="Berekening" xfId="26" builtinId="22" customBuiltin="1"/>
-    <cellStyle name="Controlecel" xfId="27" builtinId="23" customBuiltin="1"/>
-    <cellStyle name="Gekoppelde cel" xfId="35" builtinId="24" customBuiltin="1"/>
-    <cellStyle name="Goed" xfId="29" builtinId="26" customBuiltin="1"/>
-    <cellStyle name="Invoer" xfId="34" builtinId="20" customBuiltin="1"/>
-    <cellStyle name="Kop 1" xfId="30" builtinId="16" customBuiltin="1"/>
-    <cellStyle name="Kop 2" xfId="31" builtinId="17" customBuiltin="1"/>
-    <cellStyle name="Kop 3" xfId="32" builtinId="18" customBuiltin="1"/>
-    <cellStyle name="Kop 4" xfId="33" builtinId="19" customBuiltin="1"/>
-    <cellStyle name="Neutraal" xfId="36" builtinId="28" customBuiltin="1"/>
-    <cellStyle name="Notitie" xfId="37" builtinId="10" customBuiltin="1"/>
-    <cellStyle name="Ongeldig" xfId="25" builtinId="27" customBuiltin="1"/>
-    <cellStyle name="Procent" xfId="42" builtinId="5"/>
-    <cellStyle name="Standaard" xfId="0" builtinId="0"/>
-    <cellStyle name="Titel" xfId="39" builtinId="15" customBuiltin="1"/>
-    <cellStyle name="Totaal" xfId="40" builtinId="25" customBuiltin="1"/>
-    <cellStyle name="Uitvoer" xfId="38" builtinId="21" customBuiltin="1"/>
-    <cellStyle name="Verklarende tekst" xfId="28" builtinId="53" customBuiltin="1"/>
-    <cellStyle name="Waarschuwingstekst" xfId="41" builtinId="11" customBuiltin="1"/>
+    <cellStyle name="Bad" xfId="25" builtinId="27" customBuiltin="1"/>
+    <cellStyle name="Calculation" xfId="26" builtinId="22" customBuiltin="1"/>
+    <cellStyle name="Check Cell" xfId="27" builtinId="23" customBuiltin="1"/>
+    <cellStyle name="Explanatory Text" xfId="28" builtinId="53" customBuiltin="1"/>
+    <cellStyle name="Good" xfId="29" builtinId="26" customBuiltin="1"/>
+    <cellStyle name="Heading 1" xfId="30" builtinId="16" customBuiltin="1"/>
+    <cellStyle name="Heading 2" xfId="31" builtinId="17" customBuiltin="1"/>
+    <cellStyle name="Heading 3" xfId="32" builtinId="18" customBuiltin="1"/>
+    <cellStyle name="Heading 4" xfId="33" builtinId="19" customBuiltin="1"/>
+    <cellStyle name="Input" xfId="34" builtinId="20" customBuiltin="1"/>
+    <cellStyle name="Linked Cell" xfId="35" builtinId="24" customBuiltin="1"/>
+    <cellStyle name="Neutral" xfId="36" builtinId="28" customBuiltin="1"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Note" xfId="37" builtinId="10" customBuiltin="1"/>
+    <cellStyle name="Output" xfId="38" builtinId="21" customBuiltin="1"/>
+    <cellStyle name="Percent" xfId="42" builtinId="5"/>
+    <cellStyle name="Title" xfId="39" builtinId="15" customBuiltin="1"/>
+    <cellStyle name="Total" xfId="40" builtinId="25" customBuiltin="1"/>
+    <cellStyle name="Warning Text" xfId="41" builtinId="11" customBuiltin="1"/>
   </cellStyles>
   <dxfs count="2">
     <dxf>
@@ -800,10 +812,6 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1161,22 +1169,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD14F261-F35D-4366-9985-5F1DFE201882}">
-  <dimension ref="A1:L12"/>
+  <dimension ref="A1:O15"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="31.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="2" spans="1:12" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
-      <c r="J2" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="L2" t="s">
+    <row r="1" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="2" spans="1:15" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+      <c r="M2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="O2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:12" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="B3" s="2">
         <v>2016</v>
       </c>
@@ -1198,43 +1206,64 @@
       <c r="H3" s="2">
         <v>2022</v>
       </c>
-      <c r="I3" s="2"/>
-    </row>
-    <row r="4" spans="1:12" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+      <c r="I3" s="2">
+        <v>2023</v>
+      </c>
+      <c r="J3" s="2">
+        <v>2024</v>
+      </c>
+      <c r="K3" s="2">
+        <v>2025</v>
+      </c>
+      <c r="L3" s="2"/>
+    </row>
+    <row r="4" spans="1:15" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B4" s="3">
+        <f>Performance!C16</f>
+        <v>7.5140983218559262E-2</v>
+      </c>
+      <c r="C4" s="4">
+        <f>Performance!C15</f>
+        <v>0.22412749348054314</v>
+      </c>
+      <c r="D4" s="3">
+        <f>Performance!C14</f>
+        <v>-8.6303878322788297E-2</v>
+      </c>
+      <c r="E4" s="3">
+        <f>Performance!C13</f>
+        <v>0.27917737497303208</v>
+      </c>
+      <c r="F4" s="3">
         <f>Performance!C12</f>
-        <v>7.5140983218559262E-2</v>
-      </c>
-      <c r="C4" s="4">
+        <v>0.16096312460701989</v>
+      </c>
+      <c r="G4" s="3">
         <f>Performance!C11</f>
-        <v>0.22412749348054314</v>
-      </c>
-      <c r="D4" s="3">
+        <v>0.21934845882119067</v>
+      </c>
+      <c r="H4" s="3">
         <f>Performance!C10</f>
-        <v>-8.6303878322788297E-2</v>
-      </c>
-      <c r="E4" s="3">
+        <v>-0.18019401119504377</v>
+      </c>
+      <c r="I4" s="3">
         <f>Performance!C9</f>
-        <v>0.27917737497303208</v>
-      </c>
-      <c r="F4" s="3">
+        <v>0.23960000000000001</v>
+      </c>
+      <c r="J4" s="3">
         <f>Performance!C8</f>
-        <v>0.16096312460701989</v>
-      </c>
-      <c r="G4" s="3">
+        <v>0.18759999999999999</v>
+      </c>
+      <c r="K4" s="3">
         <f>Performance!C7</f>
-        <v>0.21934845882119067</v>
-      </c>
-      <c r="H4" s="3">
-        <f>Performance!C6</f>
-        <v>-0.18019401119504377</v>
-      </c>
-      <c r="I4" s="3"/>
-    </row>
-    <row r="5" spans="1:12" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+        <v>0.2117</v>
+      </c>
+      <c r="L4" s="3"/>
+    </row>
+    <row r="5" spans="1:15" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
@@ -1259,14 +1288,23 @@
       <c r="H5" s="3">
         <v>-0.17730000000000001</v>
       </c>
-      <c r="I5" s="3"/>
-    </row>
-    <row r="6" spans="1:12" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+      <c r="I5" s="3">
+        <v>0.2442</v>
+      </c>
+      <c r="J5" s="3">
+        <v>0.19189999999999999</v>
+      </c>
+      <c r="K5" s="3">
+        <v>0.216</v>
+      </c>
+      <c r="L5" s="3"/>
+    </row>
+    <row r="6" spans="1:15" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B6" s="3">
-        <f t="shared" ref="B6:H6" si="0">B5-B4</f>
+        <f t="shared" ref="B6:K6" si="0">B5-B4</f>
         <v>6.3590167814407406E-3</v>
       </c>
       <c r="C6" s="3">
@@ -1293,13 +1331,25 @@
         <f t="shared" si="0"/>
         <v>2.8940111950437608E-3</v>
       </c>
-      <c r="I6" s="3"/>
+      <c r="I6" s="3">
+        <f t="shared" si="0"/>
+        <v>4.599999999999993E-3</v>
+      </c>
       <c r="J6" s="3">
-        <f>AVERAGE(D6:G6)</f>
-        <v>4.3287299803864109E-3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.2">
+        <f t="shared" si="0"/>
+        <v>4.2999999999999983E-3</v>
+      </c>
+      <c r="K6" s="3">
+        <f t="shared" si="0"/>
+        <v>4.2999999999999983E-3</v>
+      </c>
+      <c r="L6" s="3"/>
+      <c r="M6" s="3">
+        <f>AVERAGE(D6:K6)</f>
+        <v>4.1761163895736742E-3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
       <c r="D7" s="3"/>
@@ -1309,8 +1359,11 @@
       <c r="H7" s="3"/>
       <c r="I7" s="3"/>
       <c r="J7" s="3"/>
-    </row>
-    <row r="8" spans="1:12" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+      <c r="K7" s="3"/>
+      <c r="L7" s="3"/>
+      <c r="M7" s="3"/>
+    </row>
+    <row r="8" spans="1:15" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>6</v>
       </c>
@@ -1328,11 +1381,22 @@
       <c r="G8" s="3">
         <v>1.9E-3</v>
       </c>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3"/>
-      <c r="J8" s="3"/>
-    </row>
-    <row r="9" spans="1:12" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+      <c r="H8" s="3">
+        <v>1.9E-3</v>
+      </c>
+      <c r="I8" s="3">
+        <v>1.9E-3</v>
+      </c>
+      <c r="J8" s="3">
+        <v>1.9E-3</v>
+      </c>
+      <c r="K8" s="3">
+        <v>1.9E-3</v>
+      </c>
+      <c r="L8" s="3"/>
+      <c r="M8" s="3"/>
+    </row>
+    <row r="9" spans="1:15" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>8</v>
       </c>
@@ -1354,17 +1418,29 @@
         <f>G6-G8</f>
         <v>2.2515411788093373E-3</v>
       </c>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3"/>
+      <c r="H9" s="3">
+        <f t="shared" ref="H9:K9" si="1">H6-H8</f>
+        <v>9.9401119504376081E-4</v>
+      </c>
+      <c r="I9" s="3">
+        <f t="shared" si="1"/>
+        <v>2.6999999999999932E-3</v>
+      </c>
       <c r="J9" s="3">
-        <f>AVERAGE(D9:G9)</f>
-        <v>2.4287299803864111E-3</v>
-      </c>
-      <c r="L9" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>2.3999999999999985E-3</v>
+      </c>
+      <c r="K9" s="3">
+        <f t="shared" si="1"/>
+        <v>2.3999999999999985E-3</v>
+      </c>
+      <c r="L9" s="3"/>
+      <c r="M9" s="3">
+        <f>AVERAGE(D9:K9)</f>
+        <v>2.2761163895736744E-3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A10" s="2"/>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
@@ -1375,34 +1451,51 @@
       <c r="H10" s="3"/>
       <c r="I10" s="3"/>
       <c r="J10" s="3"/>
-      <c r="L10" s="1" t="s">
+      <c r="K10" s="3"/>
+      <c r="L10" s="3"/>
+      <c r="M10" s="3"/>
+    </row>
+    <row r="11" spans="1:15" ht="15" x14ac:dyDescent="0.25">
+      <c r="A11" s="2"/>
+      <c r="F11" s="17"/>
+      <c r="G11" s="17"/>
+      <c r="H11" s="17"/>
+      <c r="I11" s="17"/>
+      <c r="J11" s="17"/>
+      <c r="K11" s="17"/>
+    </row>
+    <row r="12" spans="1:15" ht="15" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" s="17">
+        <v>2.5999999999999999E-3</v>
+      </c>
+      <c r="C12" t="s">
+        <v>14</v>
+      </c>
+      <c r="F12" s="17"/>
+      <c r="G12" s="17"/>
+      <c r="H12" s="17"/>
+      <c r="I12" s="17"/>
+      <c r="J12" s="17"/>
+      <c r="K12" s="17"/>
+    </row>
+    <row r="13" spans="1:15" ht="15" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" s="17">
+        <f>M9</f>
+        <v>2.2761163895736744E-3</v>
+      </c>
+      <c r="D13" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="15" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F11" s="18"/>
-      <c r="G11" s="18">
-        <v>0.21959999999999999</v>
-      </c>
-      <c r="H11" s="18">
-        <v>-0.17860000000000001</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" ht="15" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F12" s="18"/>
-      <c r="G12" s="18">
-        <f t="shared" ref="G12:H12" si="1">G4-G11</f>
-        <v>-2.5154117880932247E-4</v>
-      </c>
-      <c r="H12" s="18">
-        <f t="shared" si="1"/>
-        <v>-1.5940111950437652E-3</v>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A15" s="1" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -1412,7 +1505,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="36.125" style="7" customWidth="1"/>
@@ -1422,7 +1515,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="118.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="6"/>
-      <c r="B1" s="17"/>
+      <c r="B1" s="18"/>
     </row>
     <row r="2" spans="1:4" ht="27" x14ac:dyDescent="0.4">
       <c r="A2" s="8" t="s">
@@ -1440,101 +1533,137 @@
         <v>2</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D5" s="10"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A6" s="14">
+      <c r="A6" s="19"/>
+      <c r="B6" s="19"/>
+      <c r="C6" s="10"/>
+      <c r="D6" s="10"/>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A7" s="19">
+        <v>2025</v>
+      </c>
+      <c r="B7" s="19"/>
+      <c r="C7" s="20">
+        <v>0.2117</v>
+      </c>
+      <c r="D7" s="10"/>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A8" s="19">
+        <v>2024</v>
+      </c>
+      <c r="B8" s="19"/>
+      <c r="C8" s="20">
+        <v>0.18759999999999999</v>
+      </c>
+      <c r="D8" s="10"/>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A9" s="19">
+        <v>2023</v>
+      </c>
+      <c r="B9" s="19"/>
+      <c r="C9" s="20">
+        <v>0.23960000000000001</v>
+      </c>
+      <c r="D9" s="10"/>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A10" s="14">
         <v>44925</v>
       </c>
-      <c r="B6" s="11">
+      <c r="B10" s="11">
         <v>78.443299999999994</v>
       </c>
-      <c r="C6" s="12">
-        <f t="shared" ref="C6:C12" si="0">(B6-B7)/B7</f>
+      <c r="C10" s="12">
+        <f t="shared" ref="C10:C16" si="0">(B10-B11)/B11</f>
         <v>-0.18019401119504377</v>
       </c>
-      <c r="D6" s="10"/>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A7" s="15">
+      <c r="D10" s="10"/>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A11" s="15">
         <v>44561</v>
       </c>
-      <c r="B7" s="11">
+      <c r="B11" s="11">
         <v>95.685199999999995</v>
       </c>
-      <c r="C7" s="12">
+      <c r="C11" s="12">
         <f t="shared" si="0"/>
         <v>0.21934845882119067</v>
       </c>
-      <c r="D7" s="10"/>
-    </row>
-    <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="15">
+      <c r="D11" s="10"/>
+    </row>
+    <row r="12" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="15">
         <v>44196</v>
       </c>
-      <c r="B8" s="11">
+      <c r="B12" s="11">
         <v>78.472399999999993</v>
       </c>
-      <c r="C8" s="12">
+      <c r="C12" s="12">
         <f t="shared" si="0"/>
         <v>0.16096312460701989</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="15">
+    <row r="13" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="15">
         <v>43830</v>
       </c>
-      <c r="B9" s="11">
+      <c r="B13" s="11">
         <v>67.592500000000001</v>
       </c>
-      <c r="C9" s="12">
+      <c r="C13" s="12">
         <f t="shared" si="0"/>
         <v>0.27917737497303208</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="15">
+    <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="15">
         <v>43465</v>
       </c>
-      <c r="B10" s="11">
+      <c r="B14" s="11">
         <v>52.840600000000002</v>
       </c>
-      <c r="C10" s="12">
+      <c r="C14" s="12">
         <f t="shared" si="0"/>
         <v>-8.6303878322788297E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="15">
+    <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="15">
         <v>43098</v>
       </c>
-      <c r="B11" s="11">
+      <c r="B15" s="11">
         <v>57.831699999999998</v>
       </c>
-      <c r="C11" s="12">
+      <c r="C15" s="12">
         <f t="shared" si="0"/>
         <v>0.22412749348054314</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A12" s="16">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A16" s="16">
         <v>42734</v>
       </c>
-      <c r="B12" s="13">
+      <c r="B16" s="13">
         <v>47.243200000000002</v>
       </c>
-      <c r="C12" s="12">
+      <c r="C16" s="12">
         <f t="shared" si="0"/>
         <v>7.5140983218559262E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A13" s="16">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A17" s="16">
         <v>42369</v>
       </c>
-      <c r="B13" s="13">
+      <c r="B17" s="13">
         <v>43.941400000000002</v>
       </c>
     </row>
